--- a/publications.xlsx
+++ b/publications.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10404"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ghe/Documents/GitHub/quarto-academic-website-template/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/bayleighbaldwin/Downloads/researchsite/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82DFC406-A80B-A440-998C-5F77B7D5D078}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88348F79-7A9D-A242-950C-7DE2402A45E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="780" windowWidth="34200" windowHeight="19940" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="8780" yWindow="760" windowWidth="29400" windowHeight="17480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Publications" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="30">
   <si>
     <t>Section</t>
   </si>
@@ -97,95 +97,26 @@
     <t>Selected Work</t>
   </si>
   <si>
-    <t>Nature</t>
-  </si>
-  <si>
-    <t>Helveston, John, **Gang He**\*, and Michael Davidson</t>
-  </si>
-  <si>
-    <t>2022-10-26</t>
-  </si>
-  <si>
-    <t>Quantifying the Cost Savings of Global Solar Photovoltaic Supply Chains</t>
-  </si>
-  <si>
-    <t>https://drganghe.github.io/posts/2022-10-nature-cost-savings-of-global-solar-pv-value-chains/index.html</t>
-  </si>
-  <si>
-    <t>83-87</t>
-  </si>
-  <si>
-    <t>10.1038/s41586-022-05316-6</t>
-  </si>
-  <si>
-    <t>https://drganghe.github.io/files/papers/2022-nature-solar-supply-chains-preprint.pdf</t>
-  </si>
-  <si>
-    <t>https://rdcu.be/enuBz</t>
-  </si>
-  <si>
-    <t>https://github.com/jhelvy/solar-learning-2021</t>
-  </si>
-  <si>
-    <t>[IAMC2022 Best Poster Award](https://drganghe.github.io/posts/2022-12-iamc-2022-best-poster-award/index.html)</t>
-  </si>
-  <si>
-    <t>[SBU News](https://news.stonybrook.edu/environmental-stewardship/international-collaboration-is-key-to-addressing-global-climate-change/) | [GWU News](https://mediarelations.gwu.edu/global-collaboration-saved-countries-67-billion-solar-panel-production-costs) | [UCSD News](https://today.ucsd.edu/story/open-trade-saves-countries-billions-in-solar-panel-production) | [*Nature* Research Highlights](https://web.archive.org/web/20230603073317/https://www.natureasia.com/en/research/highlight/14262) | [*E&amp;E News*](https://www.eenews.net/articles/how-bidens-made-in-america-solar-strategy-may-backfire/) | [*Foreign Policy*](https://foreignpolicy.com/2023/09/21/us-china-climate-cooperation-trade-ira-green-technology/) | [GRID News](https://web.archive.org/web/20240106093827/https://themessenger.com/grid/the-us-is-reducing-its-reliance-on-china-for-green-technology-could-that-slow-progress-on-climate-change) | [PV Magazine](https://pv-magazine-usa.com/2022/10/26/a-globalized-supply-chain-is-key-to-cutting-costs-in-solar-module-manufacturing/) | [dot.LA](https://dot.la/deglobalization-2658510850.html) | [pvbuzz](https://pvbuzz.com/new-study-quantifies-cost-savings-solar-industry-globalized-supply-chains/) | [InnovateLongIsland](https://www.innovateli.com/no-736-on-immigrants-solar-energy-supplies-and-other-american-strengths-with-lots-of-candy-to-share/) | [Mercom India](https://mercomindia.com/imposing-import-tariffs-hamper-of-solar-energy-study/) | [China News](https://www.chinanews.com.cn/cj/2022/10-27/9881042.shtml) | [Science and Technology Daily](http://www.stdaily.com/index/kejixinwen/202210/e38ea5c3a3054d87a43996d39a2924ab.shtml)</t>
-  </si>
-  <si>
-    <t>[Peking University](https://cese.pku.edu.cn/images/content/2024-03/20240325151929637875.png) | [Tsinghua University](https://mp.weixin.qq.com/s/c_Z0RHwzkjziq-QvdUzs-g) | [Harvard University](https://www.belfercenter.org/event/energy-policy-seminar-michael-davidson-decoupling-china-clean-tech) (M.D.) | ITIF (J.H.) | [Climate Change Economics Forum](https://mp.weixin.qq.com/s/teDhroPPbaA6z1pVU2JrwA)</t>
-  </si>
-  <si>
-    <t>https://github.com/switch-model/switch-china-open-model</t>
-  </si>
-  <si>
-    <t>Peer-reviewed Journal Paper</t>
-  </si>
-  <si>
-    <t>2022, selected, peer-reviewed, award, highly-cited, hot-paper, nature-series, supply-chain, solar, united-states, china, germany</t>
-  </si>
-  <si>
-    <t>https://doi.org/10.5281/zenodo.6989075</t>
-  </si>
-  <si>
-    <t>**He, Gang**\*, Jiang Lin\*, Froylan Sifuentes, Xu Liu, Nikit Abhyankar, and Amol Phadke\*</t>
-  </si>
-  <si>
-    <t>Rapid Cost Decrease of Renewables and Storage Accelerates the Decarbonization of China's Power System</t>
-  </si>
-  <si>
-    <t>https://drganghe.github.io/posts/2020-05-ncomms-rapid-re-cost/index.html</t>
-  </si>
-  <si>
-    <t>Nature Communications</t>
-  </si>
-  <si>
-    <t>10.1038/s41467-020-16184-x</t>
-  </si>
-  <si>
-    <t>https://www.nature.com/articles/s41467-020-16184-x.pdf</t>
-  </si>
-  <si>
-    <t>https://static-content.springer.com/esm/art%3A10.1038%2Fs41467-020-16184-x/MediaObjects/41467_2020_16184_MOESM1_ESM.pdf</t>
-  </si>
-  <si>
-    <t>[SBU News](https://news.stonybrook.edu/newsroom/study-shows-decrease-in-renewable-energy-costs-may-serve-as-an-accelerator-for-clean-energy-expansion/) | [LBL News](https://eta.lbl.gov/news/falling-prices-could-accelerate-china) | [*Carbon Brief* Headline](https://www.carbonbrief.org/guest-post-chinas-power-sector-could-be-10-per-cent-cheaper-in-2030-with-more-renewables) | [*InsideClimateNews*](https://insideclimatenews.org/news/04062020/inside-clean-energy-arkansas-rooftop-solar/) | [*E&amp;E News*/*ClimateWire*](https://subscriber.politicopro.com/article/eenews/1063354565) | [*Forbes*](https://www.forbes.com/sites/energyinnovation/2020/08/10/plummeting-renewable-energy-battery-prices-mean-china-could-hit-62-clean-power-and-cut-costs-11-by-2030/?sh=29fa3f2f1519) | [*Nature* News](https://www.nature.com/articles/d41586-020-02927-9)</t>
-  </si>
-  <si>
-    <t>[Asia Pacific Energy Research Centre (APERC) Annual Conference 2020](https://aperc.or.jp/presentations/event_detail.php?article_info__id=388) | [Beijing Institute of Technology](https://ceep.bit.edu.cn/xzhd/xshdyg/8c8df4e81437434fb80b7ebb8d973b4c.htm) | Dartmouth College | [Harvard Kennedy School Growth Lab](https://growthlab.hks.harvard.edu/event/research-seminar-achieving-power-sector-carbon-neutrality-in-a-low-cost-renewable-era/)</t>
-  </si>
-  <si>
-    <t>2020, selected, peer-reviewed, highly-cited, nature-series, power-system, switch-china, solar, wind, storage</t>
-  </si>
-  <si>
-    <t>2020-05-15</t>
+    <t>**Baldwin, B.**\\*, Aoki, N., Wade, L., Zellou, G.</t>
+  </si>
+  <si>
+    <t>2026-03-01</t>
+  </si>
+  <si>
+    <t>Talkin’ Country in W[a:]ne Country: Sociolinguistic Variation in Napa, California (poster)</t>
+  </si>
+  <si>
+    <t>https://bayleighbaldwin.github.io/files/posters/2026-PLC.pdf</t>
+  </si>
+  <si>
+    <t>2026, poster, united-states, country-talk, interview-data</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -228,6 +159,14 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -246,19 +185,22 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -562,8 +504,8 @@
   <dimension ref="A1:Y3"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="18" style="1" customWidth="1"/>
-    <col min="2" max="2" width="55" style="1" customWidth="1"/>
+    <col min="1" max="1" width="26.6640625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="43.6640625" style="1" customWidth="1"/>
     <col min="3" max="3" width="6" style="1" customWidth="1"/>
     <col min="4" max="4" width="18.5" style="1" customWidth="1"/>
     <col min="5" max="6" width="70" style="1" customWidth="1"/>
@@ -663,125 +605,54 @@
         <v>24</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C2" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D2" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="C2" s="1">
-        <v>2022</v>
-      </c>
-      <c r="D2" s="1" t="s">
+      <c r="E2" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="F2" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="R2"/>
+      <c r="U2" s="2"/>
+      <c r="X2" s="6" t="s">
         <v>29</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="H2" s="1">
-        <v>612</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="N2" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="P2" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="R2" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="S2" s="1">
-        <v>1</v>
-      </c>
-      <c r="T2" s="1">
-        <v>1</v>
-      </c>
-      <c r="U2" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="V2" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="W2" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="X2" s="3" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="3" spans="1:25" ht="60" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="C3" s="4">
-        <v>2020</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="G3" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="H3" s="4">
-        <v>11</v>
-      </c>
-      <c r="I3" s="4">
-        <v>1</v>
-      </c>
-      <c r="J3" s="4">
-        <v>2486</v>
-      </c>
-      <c r="K3" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="L3" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="M3" s="4"/>
-      <c r="O3" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="P3" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q3" s="4"/>
-      <c r="R3" s="4"/>
-      <c r="S3" s="4">
-        <v>1</v>
-      </c>
-      <c r="T3" s="4"/>
-      <c r="V3" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="W3" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="X3" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="Y3" s="5"/>
+      <c r="B3" s="3"/>
+      <c r="C3" s="3"/>
+      <c r="D3" s="3"/>
+      <c r="E3" s="3"/>
+      <c r="F3" s="3"/>
+      <c r="G3" s="3"/>
+      <c r="H3" s="3"/>
+      <c r="I3" s="3"/>
+      <c r="J3" s="3"/>
+      <c r="K3" s="3"/>
+      <c r="L3" s="3"/>
+      <c r="M3" s="3"/>
+      <c r="O3" s="3"/>
+      <c r="P3" s="3"/>
+      <c r="Q3" s="3"/>
+      <c r="R3" s="3"/>
+      <c r="S3" s="3"/>
+      <c r="T3" s="3"/>
+      <c r="V3" s="3"/>
+      <c r="W3" s="3"/>
+      <c r="X3" s="3"/>
+      <c r="Y3" s="4"/>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="F2" r:id="rId1" xr:uid="{9562F862-4D1F-F942-8F24-FA6AB8D04A3D}"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>

--- a/publications.xlsx
+++ b/publications.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/bayleighbaldwin/Downloads/researchsite/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88348F79-7A9D-A242-950C-7DE2402A45E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A736929F-9CD7-6D4D-AACE-981ACE9C5BB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8780" yWindow="760" windowWidth="29400" windowHeight="17480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="12440" yWindow="6320" windowWidth="29400" windowHeight="17480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Publications" sheetId="1" r:id="rId1"/>
